--- a/test/fixtures/import/date1904.xlsx
+++ b/test/fixtures/import/date1904.xlsx
@@ -32,9 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -411,10 +410,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>45296</v>
+        <v>43834</v>
       </c>
       <c r="B2" s="1">
-        <v>45296.43090277778</v>
+        <v>43834.43090277778</v>
       </c>
     </row>
   </sheetData>
